--- a/data/replant_plan.xlsx
+++ b/data/replant_plan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="196">
   <si>
     <t>Field</t>
   </si>
@@ -540,9 +540,6 @@
     <t>Low yield (44.5 &lt; 60)</t>
   </si>
   <si>
-    <t>Low yield (79.2 &lt; 80)</t>
-  </si>
-  <si>
     <t>Low yield (77.5 &lt; 80), Old ratoon</t>
   </si>
   <si>
@@ -550,9 +547,6 @@
   </si>
   <si>
     <t>Low yield (37.5 &lt; 60)</t>
-  </si>
-  <si>
-    <t>Low yield (62.3 &lt; 80)</t>
   </si>
   <si>
     <t>Low yield (78.1 &lt; 80)</t>
@@ -975,7 +969,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H127"/>
+  <dimension ref="A1:H124"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2686,7 +2680,7 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>58</v>
+        <v>130</v>
       </c>
       <c r="B101" t="s">
         <v>141</v>
@@ -2700,13 +2694,10 @@
       <c r="E101" t="s">
         <v>12</v>
       </c>
-      <c r="H101" t="s">
-        <v>36</v>
-      </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>130</v>
+        <v>174</v>
       </c>
       <c r="B102" t="s">
         <v>141</v>
@@ -2715,35 +2706,35 @@
         <v>10</v>
       </c>
       <c r="D102" t="s">
-        <v>174</v>
+        <v>148</v>
       </c>
       <c r="E102" t="s">
         <v>12</v>
+      </c>
+      <c r="H102" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
+        <v>59</v>
+      </c>
+      <c r="B103" t="s">
+        <v>141</v>
+      </c>
+      <c r="C103" t="s">
+        <v>10</v>
+      </c>
+      <c r="D103" t="s">
         <v>175</v>
       </c>
-      <c r="B103" t="s">
-        <v>141</v>
-      </c>
-      <c r="C103" t="s">
-        <v>10</v>
-      </c>
-      <c r="D103" t="s">
-        <v>148</v>
-      </c>
       <c r="E103" t="s">
         <v>12</v>
-      </c>
-      <c r="H103" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="B104" t="s">
         <v>141</v>
@@ -2760,7 +2751,7 @@
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="B105" t="s">
         <v>141</v>
@@ -2774,13 +2765,16 @@
       <c r="E105" t="s">
         <v>12</v>
       </c>
+      <c r="F105" t="s">
+        <v>178</v>
+      </c>
       <c r="H105" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>13</v>
+        <v>179</v>
       </c>
       <c r="B106" t="s">
         <v>141</v>
@@ -2789,7 +2783,7 @@
         <v>10</v>
       </c>
       <c r="D106" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E106" t="s">
         <v>12</v>
@@ -2797,7 +2791,7 @@
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B107" t="s">
         <v>141</v>
@@ -2806,21 +2800,15 @@
         <v>10</v>
       </c>
       <c r="D107" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E107" t="s">
         <v>12</v>
-      </c>
-      <c r="F107" t="s">
-        <v>180</v>
-      </c>
-      <c r="H107" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>181</v>
+        <v>74</v>
       </c>
       <c r="B108" t="s">
         <v>141</v>
@@ -2834,10 +2822,13 @@
       <c r="E108" t="s">
         <v>12</v>
       </c>
+      <c r="H108" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="B109" t="s">
         <v>141</v>
@@ -2854,7 +2845,7 @@
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="B110" t="s">
         <v>141</v>
@@ -2868,13 +2859,10 @@
       <c r="E110" t="s">
         <v>12</v>
       </c>
-      <c r="H110" t="s">
-        <v>36</v>
-      </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="B111" t="s">
         <v>141</v>
@@ -2891,7 +2879,7 @@
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>95</v>
+        <v>186</v>
       </c>
       <c r="B112" t="s">
         <v>141</v>
@@ -2900,7 +2888,7 @@
         <v>10</v>
       </c>
       <c r="D112" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E112" t="s">
         <v>12</v>
@@ -2908,7 +2896,7 @@
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>21</v>
+        <v>134</v>
       </c>
       <c r="B113" t="s">
         <v>141</v>
@@ -2917,7 +2905,7 @@
         <v>10</v>
       </c>
       <c r="D113" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="E113" t="s">
         <v>12</v>
@@ -2942,41 +2930,41 @@
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="B115" t="s">
         <v>141</v>
       </c>
       <c r="C115" t="s">
-        <v>10</v>
+        <v>131</v>
       </c>
       <c r="D115" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="E115" t="s">
-        <v>12</v>
+        <v>132</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
+        <v>191</v>
+      </c>
+      <c r="B116" t="s">
+        <v>141</v>
+      </c>
+      <c r="C116" t="s">
+        <v>131</v>
+      </c>
+      <c r="D116" t="s">
         <v>190</v>
       </c>
-      <c r="B116" t="s">
-        <v>141</v>
-      </c>
-      <c r="C116" t="s">
-        <v>10</v>
-      </c>
-      <c r="D116" t="s">
-        <v>191</v>
-      </c>
       <c r="E116" t="s">
-        <v>12</v>
+        <v>132</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>83</v>
+        <v>46</v>
       </c>
       <c r="B117" t="s">
         <v>141</v>
@@ -2985,7 +2973,7 @@
         <v>131</v>
       </c>
       <c r="D117" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E117" t="s">
         <v>132</v>
@@ -2993,7 +2981,7 @@
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>193</v>
+        <v>66</v>
       </c>
       <c r="B118" t="s">
         <v>141</v>
@@ -3002,15 +2990,21 @@
         <v>131</v>
       </c>
       <c r="D118" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E118" t="s">
         <v>132</v>
       </c>
+      <c r="F118" t="s">
+        <v>192</v>
+      </c>
+      <c r="H118" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>70</v>
+        <v>115</v>
       </c>
       <c r="B119" t="s">
         <v>141</v>
@@ -3019,18 +3013,15 @@
         <v>131</v>
       </c>
       <c r="D119" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E119" t="s">
         <v>132</v>
       </c>
-      <c r="H119" t="s">
-        <v>36</v>
-      </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B120" t="s">
         <v>141</v>
@@ -3039,7 +3030,7 @@
         <v>131</v>
       </c>
       <c r="D120" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E120" t="s">
         <v>132</v>
@@ -3047,7 +3038,7 @@
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>66</v>
+        <v>193</v>
       </c>
       <c r="B121" t="s">
         <v>141</v>
@@ -3056,21 +3047,18 @@
         <v>131</v>
       </c>
       <c r="D121" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E121" t="s">
         <v>132</v>
       </c>
-      <c r="F121" t="s">
-        <v>194</v>
-      </c>
       <c r="H121" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>115</v>
+        <v>194</v>
       </c>
       <c r="B122" t="s">
         <v>141</v>
@@ -3079,7 +3067,7 @@
         <v>131</v>
       </c>
       <c r="D122" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E122" t="s">
         <v>132</v>
@@ -3087,7 +3075,7 @@
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>44</v>
+        <v>140</v>
       </c>
       <c r="B123" t="s">
         <v>141</v>
@@ -3096,7 +3084,7 @@
         <v>131</v>
       </c>
       <c r="D123" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E123" t="s">
         <v>132</v>
@@ -3104,75 +3092,21 @@
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
+        <v>48</v>
+      </c>
+      <c r="B124" t="s">
         <v>195</v>
-      </c>
-      <c r="B124" t="s">
-        <v>141</v>
       </c>
       <c r="C124" t="s">
         <v>131</v>
       </c>
       <c r="D124" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E124" t="s">
         <v>132</v>
       </c>
       <c r="H124" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A125" t="s">
-        <v>196</v>
-      </c>
-      <c r="B125" t="s">
-        <v>141</v>
-      </c>
-      <c r="C125" t="s">
-        <v>131</v>
-      </c>
-      <c r="D125" t="s">
-        <v>192</v>
-      </c>
-      <c r="E125" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A126" t="s">
-        <v>140</v>
-      </c>
-      <c r="B126" t="s">
-        <v>141</v>
-      </c>
-      <c r="C126" t="s">
-        <v>131</v>
-      </c>
-      <c r="D126" t="s">
-        <v>192</v>
-      </c>
-      <c r="E126" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
-        <v>48</v>
-      </c>
-      <c r="B127" t="s">
-        <v>197</v>
-      </c>
-      <c r="C127" t="s">
-        <v>131</v>
-      </c>
-      <c r="D127" t="s">
-        <v>192</v>
-      </c>
-      <c r="E127" t="s">
-        <v>132</v>
-      </c>
-      <c r="H127" t="s">
         <v>36</v>
       </c>
     </row>
